--- a/artfynd/A 53627-2025 artfynd.xlsx
+++ b/artfynd/A 53627-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79189287</v>
+        <v>114571610</v>
       </c>
       <c r="B2" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221343</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grusväg N Valtorp, Vstm</t>
+          <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581983.3052295044</v>
+        <v>581807</v>
       </c>
       <c r="R2" t="n">
-        <v>6664941.651911099</v>
+        <v>6665245</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5 ex. på koordinaterna plus 3 till lite S om.</t>
+          <t>2023-04-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,39 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Grusvägkant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Åkerberg</t>
+          <t>Mårten Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Åkerberg, Thommy Åkerberg</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79189064</v>
+        <v>114571609</v>
       </c>
       <c r="B3" t="n">
-        <v>95523</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,38 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224364</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Valtorp, Vstm</t>
+          <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582005.8244925807</v>
+        <v>581571</v>
       </c>
       <c r="R3" t="n">
-        <v>6664984.541983075</v>
+        <v>6665144</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,64 +851,57 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Grusvägkant</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Åkerberg</t>
+          <t>Mårten Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Åkerberg, Thommy Åkerberg</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114567650</v>
+        <v>114567429</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -976,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581903</v>
+        <v>581837</v>
       </c>
       <c r="R4" t="n">
-        <v>6664949</v>
+        <v>6665113</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1032,47 +968,46 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114567424</v>
+        <v>114567620</v>
       </c>
       <c r="B5" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1083,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581506</v>
+        <v>581624</v>
       </c>
       <c r="R5" t="n">
-        <v>6665140</v>
+        <v>6665112</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,47 +1074,46 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114567649</v>
+        <v>114567622</v>
       </c>
       <c r="B6" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1190,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581790</v>
+        <v>581621</v>
       </c>
       <c r="R6" t="n">
-        <v>6665000</v>
+        <v>6665148</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,40 +1187,39 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114567619</v>
+        <v>114567623</v>
       </c>
       <c r="B7" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1297,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581622</v>
+        <v>581566</v>
       </c>
       <c r="R7" t="n">
-        <v>6664977</v>
+        <v>6665181</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,15 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114567647</v>
+        <v>114567629</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,11 +1321,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1408,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581798</v>
+        <v>581628</v>
       </c>
       <c r="R8" t="n">
-        <v>6665083</v>
+        <v>6665085</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,12 +1398,7 @@
         <v>114567646</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,15 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114567652</v>
+        <v>114567647</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1531,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1630,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581898</v>
+        <v>581798</v>
       </c>
       <c r="R10" t="n">
-        <v>6664929</v>
+        <v>6665083</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,40 +1607,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114567641</v>
+        <v>114567648</v>
       </c>
       <c r="B11" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1737,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581493</v>
+        <v>581813</v>
       </c>
       <c r="R11" t="n">
-        <v>6665284</v>
+        <v>6664934</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,15 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114567648</v>
+        <v>114567652</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1743,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1848,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581813</v>
+        <v>581898</v>
       </c>
       <c r="R12" t="n">
-        <v>6664934</v>
+        <v>6664929</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,15 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114567429</v>
+        <v>114635825</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,23 +1849,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Munga-Horndal, Vstm</t>
+          <t>Gillmyrtorp, ca 300 m N om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581837</v>
+        <v>581812</v>
       </c>
       <c r="R13" t="n">
-        <v>6665113</v>
+        <v>6664933</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,6 +1894,11 @@
           <t>Möklinta</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>U-Sal-0812</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
           <t>2023-04-15</t>
@@ -2010,27 +1922,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mårten Nilsson</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114635825</v>
+        <v>114635864</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +1968,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2074,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581812</v>
+        <v>581899</v>
       </c>
       <c r="R14" t="n">
-        <v>6664933</v>
+        <v>6664928</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,7 +2015,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>U-Sal-0812</t>
+          <t>U-Sal-0813</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2140,68 +2051,55 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Inventering längs blivande kraftledning Munga-Horndal, Floraväkteri Sverige</t>
+          <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114635864</v>
+        <v>114567628</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gillmyrtorp, ca 300 m N om (knärot), Vstm</t>
+          <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581899</v>
+        <v>581627</v>
       </c>
       <c r="R15" t="n">
-        <v>6664928</v>
+        <v>6665085</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,11 +2124,6 @@
           <t>Möklinta</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>U-Sal-0813</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>2023-04-15</t>
@@ -2254,7 +2147,7 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Mårten Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -2262,11 +2155,1266 @@
           <t>Johan Kjetselberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
-        </is>
-      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>79189287</v>
+      </c>
+      <c r="B16" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Grusväg N Valtorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>581983</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6664942</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-07-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-07-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>5 ex. på koordinaterna plus 3 till lite S om.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Grusvägkant</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michael Åkerberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Åkerberg, Thommy Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114567424</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>581506</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6665140</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114567619</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>581622</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6664977</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114567621</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>581623</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6665117</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114567627</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>581692</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6665047</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114567641</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>581493</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6665284</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114567649</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>581790</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6665000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114567650</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>581903</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6664949</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114567681</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>581615</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6665206</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114567682</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>581657</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6665305</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>114568809</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>581497</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6665110</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>79189064</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>N Valtorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>582006</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6664985</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2019-07-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2019-07-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Grusvägkant</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Michael Åkerberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Michael Åkerberg, Thommy Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53627-2025 artfynd.xlsx
+++ b/artfynd/A 53627-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571610</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571609</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567429</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567620</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567622</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567623</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567629</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567646</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567647</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,6 +1760,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567648</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1816,6 +1871,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567652</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1935,6 +1995,11 @@
           <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114635825</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2052,6 +2117,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114635864</t>
         </is>
       </c>
     </row>
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567628</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2276,6 +2351,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79189287</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2378,6 +2458,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567424</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2480,6 +2565,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567619</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2582,6 +2672,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567621</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2684,6 +2779,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567627</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2786,6 +2886,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567641</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2888,6 +2993,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567649</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2990,6 +3100,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567650</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3096,6 +3211,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567681</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3202,6 +3322,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567682</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3308,6 +3433,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114568809</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3415,8 +3545,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79189064</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>